--- a/sanchez_Ex3A_tables.xlsx
+++ b/sanchez_Ex3A_tables.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dahliasanchez\Documents\W2_Workshop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{947C32BD-6F4E-4A3A-A6C9-A8B650DFEE15}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C6268AF-56B3-4C1D-A24B-34E054DAF211}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-90" yWindow="0" windowWidth="9780" windowHeight="11370" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1700" yWindow="2330" windowWidth="14400" windowHeight="8170" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Customer" sheetId="4" r:id="rId1"/>
@@ -144,7 +144,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -163,6 +163,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -177,7 +183,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
@@ -185,6 +191,7 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="17" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -519,52 +526,59 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A4:F5"/>
+  <dimension ref="A1:F5"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="8.453125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="7.90625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F1" s="4" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2" s="5">
+        <v>46120</v>
+      </c>
+      <c r="C2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D2" t="s">
+        <v>15</v>
+      </c>
+      <c r="E2" t="s">
+        <v>17</v>
+      </c>
+      <c r="F2">
+        <v>1</v>
+      </c>
+    </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A4" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="B4" t="s">
-        <v>10</v>
-      </c>
-      <c r="C4" t="s">
-        <v>11</v>
-      </c>
-      <c r="D4" t="s">
-        <v>12</v>
-      </c>
-      <c r="E4" t="s">
-        <v>13</v>
-      </c>
-      <c r="F4" s="4" t="s">
-        <v>14</v>
-      </c>
+      <c r="A4" s="7"/>
+      <c r="F4" s="7"/>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A5">
-        <v>1</v>
-      </c>
-      <c r="B5" s="5">
-        <v>46120</v>
-      </c>
-      <c r="C5" t="s">
-        <v>16</v>
-      </c>
-      <c r="D5" t="s">
-        <v>15</v>
-      </c>
-      <c r="E5" t="s">
-        <v>17</v>
-      </c>
-      <c r="F5">
-        <v>1</v>
-      </c>
+      <c r="B5" s="5"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
